--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/CALIFORNIA_2022.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/CALIFORNIA_2022.xlsx
@@ -3073,7 +3073,7 @@
         <v>144</v>
       </c>
       <c r="D151">
-        <v>0.0009047158312704975</v>
+        <v>0.0009047158312704976</v>
       </c>
     </row>
     <row r="152">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C202">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C251">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C407">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C417">
@@ -13441,7 +13441,7 @@
         <v>147</v>
       </c>
       <c r="D727">
-        <v>0.0009235640777552995</v>
+        <v>0.0009235640777552996</v>
       </c>
     </row>
     <row r="728">
@@ -16782,7 +16782,7 @@
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C913">
@@ -19212,7 +19212,7 @@
       </c>
       <c r="B1048" t="inlineStr">
         <is>
-          <t>San Bartolome Yucane</t>
+          <t>San Bartolome Yucuane</t>
         </is>
       </c>
       <c r="C1048">
@@ -20760,7 +20760,7 @@
       </c>
       <c r="B1134" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C1134">
@@ -20778,7 +20778,7 @@
       </c>
       <c r="B1135" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1135">
@@ -22560,7 +22560,7 @@
       </c>
       <c r="B1234" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C1234">
@@ -22578,7 +22578,7 @@
       </c>
       <c r="B1235" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1235">
@@ -22657,7 +22657,7 @@
         <v>146</v>
       </c>
       <c r="D1239">
-        <v>0.0009172813289270321</v>
+        <v>0.000917281328927032</v>
       </c>
     </row>
     <row r="1240">
@@ -22776,7 +22776,7 @@
       </c>
       <c r="B1246" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C1246">
@@ -26797,7 +26797,7 @@
         <v>146</v>
       </c>
       <c r="D1469">
-        <v>0.0009172813289270321</v>
+        <v>0.000917281328927032</v>
       </c>
     </row>
     <row r="1470">
@@ -26869,7 +26869,7 @@
         <v>144</v>
       </c>
       <c r="D1473">
-        <v>0.0009047158312704975</v>
+        <v>0.0009047158312704976</v>
       </c>
     </row>
     <row r="1474">
@@ -27301,7 +27301,7 @@
         <v>151</v>
       </c>
       <c r="D1497">
-        <v>0.0009486950730683689</v>
+        <v>0.0009486950730683688</v>
       </c>
     </row>
     <row r="1498">
@@ -27445,7 +27445,7 @@
         <v>146</v>
       </c>
       <c r="D1505">
-        <v>0.0009172813289270321</v>
+        <v>0.000917281328927032</v>
       </c>
     </row>
     <row r="1506">
@@ -32071,7 +32071,7 @@
         <v>146</v>
       </c>
       <c r="D1762">
-        <v>0.0009172813289270321</v>
+        <v>0.000917281328927032</v>
       </c>
     </row>
     <row r="1763">
@@ -32089,7 +32089,7 @@
         <v>146</v>
       </c>
       <c r="D1763">
-        <v>0.0009172813289270321</v>
+        <v>0.000917281328927032</v>
       </c>
     </row>
     <row r="1764">
@@ -34926,7 +34926,7 @@
       </c>
       <c r="B1921" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1921">
